--- a/src/設備/設備類の価格.xlsx
+++ b/src/設備/設備類の価格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\kyont\private\game_modding\simutrans\128japan+\src\設備\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E0AE91-E8C8-43A7-B552-23B0BC928E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216D4FBC-338A-4B9D-B8BF-46975C13BB4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{9A382892-6161-4CE3-86B7-0F1BE08D9B19}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
   <si>
     <t>名称</t>
     <rPh sb="0" eb="2">
@@ -319,6 +319,30 @@
     <t>50km/h幹線道路</t>
     <rPh sb="6" eb="10">
       <t>カンセンドウロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>60km/h幹線道路橋</t>
+    <rPh sb="6" eb="10">
+      <t>カンセンドウロ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ハシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>瀝青</t>
+    <rPh sb="0" eb="2">
+      <t>レキセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>橋</t>
+    <rPh sb="0" eb="1">
+      <t>ハシ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -694,7 +718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DBAFF05-1A64-4ED6-A821-85E9FCBAE7BD}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.375" style="1" bestFit="1" customWidth="1"/>
@@ -964,11 +988,11 @@
         <v>1</v>
       </c>
       <c r="G9" s="1">
-        <f t="shared" ref="G9:G12" si="2">$B9*1250*$D9*$F9</f>
+        <f t="shared" ref="G9:G14" si="2">$B9*1250*$D9*$F9</f>
         <v>62500</v>
       </c>
       <c r="H9" s="1">
-        <f t="shared" ref="H9:H12" si="3">$B9*1.8*$D9*IF(1-$F9=0,1,(1-$F9)*10)</f>
+        <f t="shared" ref="H9:H14" si="3">$B9*1.8*$D9*IF(1-$F9=0,1,(1-$F9)*10)</f>
         <v>90</v>
       </c>
     </row>
@@ -1060,6 +1084,36 @@
       <c r="H12" s="1">
         <f t="shared" si="3"/>
         <v>144</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="1">
+        <v>60</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="1">
+        <f>_xlfn.XLOOKUP($C14,構造係数!$A$2:$A$5,構造係数!$B$2:$B$5)</f>
+        <v>5</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="1">
+        <f>_xlfn.XLOOKUP($E14,舗装係数!$A$2:$A$6,舗装係数!$B$2:$B$6)</f>
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="2"/>
+        <v>375000</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="3"/>
+        <v>540</v>
       </c>
     </row>
   </sheetData>

--- a/src/設備/設備類の価格.xlsx
+++ b/src/設備/設備類の価格.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\kyont\private\game_modding\simutrans\128japan+\src\設備\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216D4FBC-338A-4B9D-B8BF-46975C13BB4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D15AA0BF-C879-4512-BE22-3ECC572F56DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{9A382892-6161-4CE3-86B7-0F1BE08D9B19}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{9A382892-6161-4CE3-86B7-0F1BE08D9B19}"/>
   </bookViews>
   <sheets>
     <sheet name="道路" sheetId="1" r:id="rId1"/>
-    <sheet name="構造係数" sheetId="4" r:id="rId2"/>
-    <sheet name="舗装係数" sheetId="5" r:id="rId3"/>
+    <sheet name="停留所" sheetId="6" r:id="rId2"/>
+    <sheet name="構造係数" sheetId="4" r:id="rId3"/>
+    <sheet name="舗装係数" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,8 +33,202 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>林田光惺</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{AC7AF950-B1AA-4B43-81C0-E6CA4E4B92B7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>林田光惺:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+enables_pax</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{3A61B7D9-D532-45DC-850A-E32AC5212B12}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>林田光惺:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+enables_post
+enables_ware
+↑当paksetにおいてこれらは同時に有効であるべきである。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{EB9F6093-AF4B-4B49-88AD-0F438308F0D6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>林田光惺:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+allow_underground</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{3BD7C26C-A1E4-4065-8238-F3F458B4C9DF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>林田光惺:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+Level</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{61529259-14C2-4ECF-91B5-D785880D37DE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>林田光惺:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+一本の柱に何枚かの板を貼り付けた簡易的なバス停。だるま型とも呼ばれる。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A11" authorId="0" shapeId="0" xr:uid="{66778456-577D-40F4-9504-C5AC7E47FD90}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>林田光惺:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+2本の曲がった柱に板を挟み込むようにして作られたバス停。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A20" authorId="0" shapeId="0" xr:uid="{50040DA9-A18C-4C25-ABCD-E290D611564F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>林田光惺:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+1本の柱の上に直方体が載った本格的なバス停。金星型、明星型などとも呼ばれる。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="75">
   <si>
     <t>名称</t>
     <rPh sb="0" eb="2">
@@ -343,6 +538,340 @@
     <t>橋</t>
     <rPh sb="0" eb="1">
       <t>ハシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>旅客</t>
+    <rPh sb="0" eb="2">
+      <t>リョカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>郵便/貨物</t>
+    <rPh sb="0" eb="2">
+      <t>ユウビン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カモツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>地上</t>
+    <rPh sb="0" eb="2">
+      <t>チジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>地下</t>
+    <rPh sb="0" eb="2">
+      <t>チカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レベル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>標準価格</t>
+    <rPh sb="0" eb="4">
+      <t>ヒョウジュンカカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しらゆり型</t>
+    <rPh sb="4" eb="5">
+      <t>ガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行灯型</t>
+    <rPh sb="0" eb="3">
+      <t>アンドンガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>郵便ポスト</t>
+    <rPh sb="0" eb="2">
+      <t>ユウビン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>荷役所</t>
+    <rPh sb="0" eb="2">
+      <t>ニヤク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収容数</t>
+    <rPh sb="0" eb="3">
+      <t>シュウヨウスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しらゆり型ポスト付き</t>
+    <rPh sb="4" eb="5">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しらゆり型ベンチ付き</t>
+    <rPh sb="4" eb="5">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しらゆり型ベンチ・ポスト付き</t>
+    <rPh sb="4" eb="5">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しらゆり型屋根付き</t>
+    <rPh sb="4" eb="5">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ヤネツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しらゆり型屋根・ポスト付き</t>
+    <rPh sb="4" eb="5">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヤネ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しらゆり型屋根・ベンチ付き</t>
+    <rPh sb="4" eb="5">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヤネ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しらゆり型屋根・ベンチ・ポスト付き</t>
+    <rPh sb="4" eb="5">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヤネ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行灯型ポスト付き</t>
+    <rPh sb="0" eb="3">
+      <t>アンドンガタ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行灯型ベンチ付き</t>
+    <rPh sb="0" eb="3">
+      <t>アンドンガタ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行灯型ベンチ・ポスト付き</t>
+    <rPh sb="0" eb="3">
+      <t>アンドンガタ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行灯型屋根付き</t>
+    <rPh sb="0" eb="3">
+      <t>アンドンガタ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ヤネツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行灯型屋根・ポスト付き</t>
+    <rPh sb="0" eb="3">
+      <t>アンドンガタ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヤネ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行灯型屋根・ベンチ付き</t>
+    <rPh sb="0" eb="3">
+      <t>アンドンガタ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヤネ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行灯型屋根・ベンチ・ポスト付き</t>
+    <rPh sb="0" eb="3">
+      <t>アンドンガタ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヤネ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ひまわり型</t>
+    <rPh sb="4" eb="5">
+      <t>ガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ひまわり型ポスト付き</t>
+    <rPh sb="4" eb="5">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ひまわり型ベンチ付き</t>
+    <rPh sb="4" eb="5">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ひまわり型ベンチ・ポスト付き</t>
+    <rPh sb="4" eb="5">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ひまわり型屋根付き</t>
+    <rPh sb="4" eb="5">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ヤネツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ひまわり型屋根・ポスト付き</t>
+    <rPh sb="4" eb="5">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヤネ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ひまわり型屋根・ベンチ付き</t>
+    <rPh sb="4" eb="5">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヤネ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ひまわり型屋根・ベンチ・ポスト付き</t>
+    <rPh sb="4" eb="5">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヤネ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>地上/地下</t>
+    <rPh sb="0" eb="2">
+      <t>チジョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>チカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -351,7 +880,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -370,6 +899,21 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="MS P ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="MS P ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -719,7 +1263,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DBAFF05-1A64-4ED6-A821-85E9FCBAE7BD}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="20.375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" bestFit="1" customWidth="1"/>
@@ -730,7 +1274,7 @@
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -756,7 +1300,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
@@ -786,7 +1330,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
@@ -816,7 +1360,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>34</v>
       </c>
@@ -846,7 +1390,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
@@ -876,7 +1420,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
         <v>37</v>
       </c>
@@ -906,7 +1450,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
         <v>23</v>
       </c>
@@ -936,7 +1480,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
         <v>28</v>
       </c>
@@ -966,7 +1510,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
         <v>29</v>
       </c>
@@ -996,7 +1540,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1026,7 +1570,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
         <v>30</v>
       </c>
@@ -1056,7 +1600,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
@@ -1086,7 +1630,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
@@ -1132,14 +1676,897 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D96AB7C-2EF5-4666-9715-C38F002C0756}">
+  <dimension ref="A1:I30"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="33.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="5.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="7.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <f>IF($D2=1,IF($E2=1,2,0),IF($E2=1,1,"-無効な値-"))</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1">
+        <f>32*$G2</f>
+        <v>32</v>
+      </c>
+      <c r="I2" s="1">
+        <f t="shared" ref="I2:I30" si="0">$G2*700</f>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
+        <f t="shared" ref="F3:F30" si="1">IF($D3=1,IF($E3=1,2,0),IF($E3=1,1,"-無効な値-"))</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
+      <c r="H3" s="1">
+        <f>32*$G3</f>
+        <v>64</v>
+      </c>
+      <c r="I3" s="1">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>3</v>
+      </c>
+      <c r="H4" s="1">
+        <f>32*$G4</f>
+        <v>96</v>
+      </c>
+      <c r="I4" s="1">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>4</v>
+      </c>
+      <c r="H5" s="1">
+        <f>32*$G5</f>
+        <v>128</v>
+      </c>
+      <c r="I5" s="1">
+        <f t="shared" si="0"/>
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>5</v>
+      </c>
+      <c r="H6" s="1">
+        <f>32*$G6</f>
+        <v>160</v>
+      </c>
+      <c r="I6" s="1">
+        <f t="shared" si="0"/>
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>6</v>
+      </c>
+      <c r="H7" s="1">
+        <f>32*$G7</f>
+        <v>192</v>
+      </c>
+      <c r="I7" s="1">
+        <f t="shared" si="0"/>
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>7</v>
+      </c>
+      <c r="H8" s="1">
+        <f>32*$G8</f>
+        <v>224</v>
+      </c>
+      <c r="I8" s="1">
+        <f t="shared" si="0"/>
+        <v>4900</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>8</v>
+      </c>
+      <c r="H9" s="1">
+        <f>32*$G9</f>
+        <v>256</v>
+      </c>
+      <c r="I9" s="1">
+        <f t="shared" si="0"/>
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>2</v>
+      </c>
+      <c r="H11" s="1">
+        <f>32*$G11</f>
+        <v>64</v>
+      </c>
+      <c r="I11" s="1">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>3</v>
+      </c>
+      <c r="H12" s="1">
+        <f>32*$G12</f>
+        <v>96</v>
+      </c>
+      <c r="I12" s="1">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>4</v>
+      </c>
+      <c r="H13" s="1">
+        <f>32*$G13</f>
+        <v>128</v>
+      </c>
+      <c r="I13" s="1">
+        <f t="shared" si="0"/>
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>5</v>
+      </c>
+      <c r="H14" s="1">
+        <f>32*$G14</f>
+        <v>160</v>
+      </c>
+      <c r="I14" s="1">
+        <f t="shared" si="0"/>
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="1">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>6</v>
+      </c>
+      <c r="H15" s="1">
+        <f>32*$G15</f>
+        <v>192</v>
+      </c>
+      <c r="I15" s="1">
+        <f t="shared" si="0"/>
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="1">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>7</v>
+      </c>
+      <c r="H16" s="1">
+        <f>32*$G16</f>
+        <v>224</v>
+      </c>
+      <c r="I16" s="1">
+        <f t="shared" si="0"/>
+        <v>4900</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>8</v>
+      </c>
+      <c r="H17" s="1">
+        <f>32*$G17</f>
+        <v>256</v>
+      </c>
+      <c r="I17" s="1">
+        <f t="shared" si="0"/>
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>9</v>
+      </c>
+      <c r="H18" s="1">
+        <f>32*$G18</f>
+        <v>288</v>
+      </c>
+      <c r="I18" s="1">
+        <f t="shared" si="0"/>
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>3</v>
+      </c>
+      <c r="H20" s="1">
+        <f>32*$G20</f>
+        <v>96</v>
+      </c>
+      <c r="I20" s="1">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>4</v>
+      </c>
+      <c r="H21" s="1">
+        <f>32*$G21</f>
+        <v>128</v>
+      </c>
+      <c r="I21" s="1">
+        <f t="shared" si="0"/>
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0</v>
+      </c>
+      <c r="F22" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>5</v>
+      </c>
+      <c r="H22" s="1">
+        <f>32*$G22</f>
+        <v>160</v>
+      </c>
+      <c r="I22" s="1">
+        <f t="shared" si="0"/>
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>6</v>
+      </c>
+      <c r="H23" s="1">
+        <f>32*$G23</f>
+        <v>192</v>
+      </c>
+      <c r="I23" s="1">
+        <f t="shared" si="0"/>
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" s="1">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>7</v>
+      </c>
+      <c r="H24" s="1">
+        <f>32*$G24</f>
+        <v>224</v>
+      </c>
+      <c r="I24" s="1">
+        <f t="shared" si="0"/>
+        <v>4900</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0</v>
+      </c>
+      <c r="F25" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>8</v>
+      </c>
+      <c r="H25" s="1">
+        <f>32*$G25</f>
+        <v>256</v>
+      </c>
+      <c r="I25" s="1">
+        <f t="shared" si="0"/>
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1</v>
+      </c>
+      <c r="C26" s="1">
+        <v>0</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0</v>
+      </c>
+      <c r="F26" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>9</v>
+      </c>
+      <c r="H26" s="1">
+        <f>32*$G26</f>
+        <v>288</v>
+      </c>
+      <c r="I26" s="1">
+        <f t="shared" si="0"/>
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" s="1">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1">
+        <v>0</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>10</v>
+      </c>
+      <c r="H27" s="1">
+        <f>32*$G27</f>
+        <v>320</v>
+      </c>
+      <c r="I27" s="1">
+        <f t="shared" si="0"/>
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="1">
+        <v>0</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0</v>
+      </c>
+      <c r="F29" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="1">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1">
+        <f>32*$G29</f>
+        <v>32</v>
+      </c>
+      <c r="I29" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="1">
+        <v>0</v>
+      </c>
+      <c r="C30" s="1">
+        <v>1</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1">
+        <v>0</v>
+      </c>
+      <c r="F30" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G30" s="1">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1">
+        <f>32*$G30</f>
+        <v>32</v>
+      </c>
+      <c r="I30" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA8ED1E-A793-430E-86B6-4402C0FDE0F0}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -1147,7 +2574,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1155,7 +2582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -1163,7 +2590,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -1171,7 +2598,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -1185,17 +2612,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D00E22B5-9D70-490B-949A-2EB9733BBAD6}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="23.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
@@ -1206,7 +2633,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -1217,7 +2644,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
@@ -1228,7 +2655,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
@@ -1236,7 +2663,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -1247,7 +2674,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="37.5" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" ht="37.5">
       <c r="A6" s="1" t="s">
         <v>22</v>
       </c>

--- a/src/設備/設備類の価格.xlsx
+++ b/src/設備/設備類の価格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\kyont\private\game_modding\simutrans\128japan+\src\設備\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D15AA0BF-C879-4512-BE22-3ECC572F56DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA06D25A-A329-4CA1-9469-4F98C850E19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{9A382892-6161-4CE3-86B7-0F1BE08D9B19}"/>
   </bookViews>
@@ -1743,11 +1743,11 @@
         <v>1</v>
       </c>
       <c r="H2" s="1">
-        <f>32*$G2</f>
+        <f t="shared" ref="H2:H9" si="0">32*$G2</f>
         <v>32</v>
       </c>
       <c r="I2" s="1">
-        <f t="shared" ref="I2:I30" si="0">$G2*700</f>
+        <f t="shared" ref="I2:I30" si="1">$G2*700</f>
         <v>700</v>
       </c>
     </row>
@@ -1768,18 +1768,18 @@
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <f t="shared" ref="F3:F30" si="1">IF($D3=1,IF($E3=1,2,0),IF($E3=1,1,"-無効な値-"))</f>
+        <f t="shared" ref="F3:F30" si="2">IF($D3=1,IF($E3=1,2,0),IF($E3=1,1,"-無効な値-"))</f>
         <v>0</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
       <c r="H3" s="1">
-        <f>32*$G3</f>
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="I3" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1400</v>
       </c>
     </row>
@@ -1800,19 +1800,19 @@
         <v>0</v>
       </c>
       <c r="F4" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>2</v>
+      </c>
+      <c r="H4" s="1">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="I4" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G4" s="1">
-        <v>3</v>
-      </c>
-      <c r="H4" s="1">
-        <f>32*$G4</f>
-        <v>96</v>
-      </c>
-      <c r="I4" s="1">
-        <f t="shared" si="0"/>
-        <v>2100</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1832,19 +1832,19 @@
         <v>0</v>
       </c>
       <c r="F5" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>3</v>
+      </c>
+      <c r="H5" s="1">
+        <f t="shared" si="0"/>
+        <v>96</v>
+      </c>
+      <c r="I5" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G5" s="1">
-        <v>4</v>
-      </c>
-      <c r="H5" s="1">
-        <f>32*$G5</f>
-        <v>128</v>
-      </c>
-      <c r="I5" s="1">
-        <f t="shared" si="0"/>
-        <v>2800</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1864,19 +1864,19 @@
         <v>0</v>
       </c>
       <c r="F6" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>2</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="I6" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="1">
-        <v>5</v>
-      </c>
-      <c r="H6" s="1">
-        <f>32*$G6</f>
-        <v>160</v>
-      </c>
-      <c r="I6" s="1">
-        <f t="shared" si="0"/>
-        <v>3500</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1896,19 +1896,19 @@
         <v>0</v>
       </c>
       <c r="F7" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>3</v>
+      </c>
+      <c r="H7" s="1">
+        <f t="shared" si="0"/>
+        <v>96</v>
+      </c>
+      <c r="I7" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="1">
-        <v>6</v>
-      </c>
-      <c r="H7" s="1">
-        <f>32*$G7</f>
-        <v>192</v>
-      </c>
-      <c r="I7" s="1">
-        <f t="shared" si="0"/>
-        <v>4200</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1928,19 +1928,19 @@
         <v>0</v>
       </c>
       <c r="F8" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>3</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="0"/>
+        <v>96</v>
+      </c>
+      <c r="I8" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G8" s="1">
-        <v>7</v>
-      </c>
-      <c r="H8" s="1">
-        <f>32*$G8</f>
-        <v>224</v>
-      </c>
-      <c r="I8" s="1">
-        <f t="shared" si="0"/>
-        <v>4900</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1960,19 +1960,19 @@
         <v>0</v>
       </c>
       <c r="F9" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>4</v>
+      </c>
+      <c r="H9" s="1">
+        <f t="shared" si="0"/>
+        <v>128</v>
+      </c>
+      <c r="I9" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G9" s="1">
-        <v>8</v>
-      </c>
-      <c r="H9" s="1">
-        <f>32*$G9</f>
-        <v>256</v>
-      </c>
-      <c r="I9" s="1">
-        <f t="shared" si="0"/>
-        <v>5600</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1992,18 +1992,18 @@
         <v>0</v>
       </c>
       <c r="F11" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G11" s="1">
         <v>2</v>
       </c>
       <c r="H11" s="1">
-        <f>32*$G11</f>
+        <f t="shared" ref="H11:H18" si="3">32*$G11</f>
         <v>64</v>
       </c>
       <c r="I11" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1400</v>
       </c>
     </row>
@@ -2024,18 +2024,18 @@
         <v>0</v>
       </c>
       <c r="F12" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G12" s="1">
         <v>3</v>
       </c>
       <c r="H12" s="1">
-        <f>32*$G12</f>
+        <f t="shared" si="3"/>
         <v>96</v>
       </c>
       <c r="I12" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2100</v>
       </c>
     </row>
@@ -2056,19 +2056,19 @@
         <v>0</v>
       </c>
       <c r="F13" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>3</v>
+      </c>
+      <c r="H13" s="1">
+        <f t="shared" si="3"/>
+        <v>96</v>
+      </c>
+      <c r="I13" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="1">
-        <v>4</v>
-      </c>
-      <c r="H13" s="1">
-        <f>32*$G13</f>
-        <v>128</v>
-      </c>
-      <c r="I13" s="1">
-        <f t="shared" si="0"/>
-        <v>2800</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -2088,19 +2088,19 @@
         <v>0</v>
       </c>
       <c r="F14" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>4</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="3"/>
+        <v>128</v>
+      </c>
+      <c r="I14" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="1">
-        <v>5</v>
-      </c>
-      <c r="H14" s="1">
-        <f>32*$G14</f>
-        <v>160</v>
-      </c>
-      <c r="I14" s="1">
-        <f t="shared" si="0"/>
-        <v>3500</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -2120,19 +2120,19 @@
         <v>0</v>
       </c>
       <c r="F15" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>3</v>
+      </c>
+      <c r="H15" s="1">
+        <f t="shared" si="3"/>
+        <v>96</v>
+      </c>
+      <c r="I15" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="1">
-        <v>6</v>
-      </c>
-      <c r="H15" s="1">
-        <f>32*$G15</f>
-        <v>192</v>
-      </c>
-      <c r="I15" s="1">
-        <f t="shared" si="0"/>
-        <v>4200</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -2152,19 +2152,19 @@
         <v>0</v>
       </c>
       <c r="F16" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>4</v>
+      </c>
+      <c r="H16" s="1">
+        <f t="shared" si="3"/>
+        <v>128</v>
+      </c>
+      <c r="I16" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="1">
-        <v>7</v>
-      </c>
-      <c r="H16" s="1">
-        <f>32*$G16</f>
-        <v>224</v>
-      </c>
-      <c r="I16" s="1">
-        <f t="shared" si="0"/>
-        <v>4900</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -2184,19 +2184,19 @@
         <v>0</v>
       </c>
       <c r="F17" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>4</v>
+      </c>
+      <c r="H17" s="1">
+        <f t="shared" si="3"/>
+        <v>128</v>
+      </c>
+      <c r="I17" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="1">
-        <v>8</v>
-      </c>
-      <c r="H17" s="1">
-        <f>32*$G17</f>
-        <v>256</v>
-      </c>
-      <c r="I17" s="1">
-        <f t="shared" si="0"/>
-        <v>5600</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -2216,19 +2216,19 @@
         <v>0</v>
       </c>
       <c r="F18" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>5</v>
+      </c>
+      <c r="H18" s="1">
+        <f t="shared" si="3"/>
+        <v>160</v>
+      </c>
+      <c r="I18" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G18" s="1">
-        <v>9</v>
-      </c>
-      <c r="H18" s="1">
-        <f>32*$G18</f>
-        <v>288</v>
-      </c>
-      <c r="I18" s="1">
-        <f t="shared" si="0"/>
-        <v>6300</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -2248,18 +2248,18 @@
         <v>0</v>
       </c>
       <c r="F20" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G20" s="1">
         <v>3</v>
       </c>
       <c r="H20" s="1">
-        <f>32*$G20</f>
+        <f t="shared" ref="H20:H27" si="4">32*$G20</f>
         <v>96</v>
       </c>
       <c r="I20" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2100</v>
       </c>
     </row>
@@ -2280,18 +2280,18 @@
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G21" s="1">
         <v>4</v>
       </c>
       <c r="H21" s="1">
-        <f>32*$G21</f>
+        <f t="shared" si="4"/>
         <v>128</v>
       </c>
       <c r="I21" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2800</v>
       </c>
     </row>
@@ -2312,19 +2312,19 @@
         <v>0</v>
       </c>
       <c r="F22" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>4</v>
+      </c>
+      <c r="H22" s="1">
+        <f t="shared" si="4"/>
+        <v>128</v>
+      </c>
+      <c r="I22" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G22" s="1">
-        <v>5</v>
-      </c>
-      <c r="H22" s="1">
-        <f>32*$G22</f>
-        <v>160</v>
-      </c>
-      <c r="I22" s="1">
-        <f t="shared" si="0"/>
-        <v>3500</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -2344,19 +2344,19 @@
         <v>0</v>
       </c>
       <c r="F23" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>5</v>
+      </c>
+      <c r="H23" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="I23" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G23" s="1">
-        <v>6</v>
-      </c>
-      <c r="H23" s="1">
-        <f>32*$G23</f>
-        <v>192</v>
-      </c>
-      <c r="I23" s="1">
-        <f t="shared" si="0"/>
-        <v>4200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -2376,19 +2376,19 @@
         <v>0</v>
       </c>
       <c r="F24" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>4</v>
+      </c>
+      <c r="H24" s="1">
+        <f t="shared" si="4"/>
+        <v>128</v>
+      </c>
+      <c r="I24" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G24" s="1">
-        <v>7</v>
-      </c>
-      <c r="H24" s="1">
-        <f>32*$G24</f>
-        <v>224</v>
-      </c>
-      <c r="I24" s="1">
-        <f t="shared" si="0"/>
-        <v>4900</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -2408,19 +2408,19 @@
         <v>0</v>
       </c>
       <c r="F25" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>5</v>
+      </c>
+      <c r="H25" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="I25" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G25" s="1">
-        <v>8</v>
-      </c>
-      <c r="H25" s="1">
-        <f>32*$G25</f>
-        <v>256</v>
-      </c>
-      <c r="I25" s="1">
-        <f t="shared" si="0"/>
-        <v>5600</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -2440,19 +2440,19 @@
         <v>0</v>
       </c>
       <c r="F26" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>5</v>
+      </c>
+      <c r="H26" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="I26" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G26" s="1">
-        <v>9</v>
-      </c>
-      <c r="H26" s="1">
-        <f>32*$G26</f>
-        <v>288</v>
-      </c>
-      <c r="I26" s="1">
-        <f t="shared" si="0"/>
-        <v>6300</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -2472,19 +2472,19 @@
         <v>0</v>
       </c>
       <c r="F27" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>6</v>
+      </c>
+      <c r="H27" s="1">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="I27" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G27" s="1">
-        <v>10</v>
-      </c>
-      <c r="H27" s="1">
-        <f>32*$G27</f>
-        <v>320</v>
-      </c>
-      <c r="I27" s="1">
-        <f t="shared" si="0"/>
-        <v>7000</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -2504,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G29" s="1">
@@ -2515,7 +2515,7 @@
         <v>32</v>
       </c>
       <c r="I29" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>700</v>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G30" s="1">
@@ -2547,7 +2547,7 @@
         <v>32</v>
       </c>
       <c r="I30" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>700</v>
       </c>
     </row>

--- a/src/設備/設備類の価格.xlsx
+++ b/src/設備/設備類の価格.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\kyont\private\game_modding\simutrans\128japan+\src\設備\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA06D25A-A329-4CA1-9469-4F98C850E19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E31FCE-0384-43B6-9891-1580E3EE8929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{9A382892-6161-4CE3-86B7-0F1BE08D9B19}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{9A382892-6161-4CE3-86B7-0F1BE08D9B19}"/>
   </bookViews>
   <sheets>
     <sheet name="道路" sheetId="1" r:id="rId1"/>
@@ -228,7 +228,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="77">
   <si>
     <t>名称</t>
     <rPh sb="0" eb="2">
@@ -872,6 +872,23 @@
     </rPh>
     <rPh sb="3" eb="5">
       <t>チカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30km/h鉄板橋</t>
+    <rPh sb="6" eb="8">
+      <t>テッパン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ハシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>橋</t>
+    <rPh sb="0" eb="1">
+      <t>ハシ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1262,7 +1279,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DBAFF05-1A64-4ED6-A821-85E9FCBAE7BD}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="20.375" style="1" bestFit="1" customWidth="1"/>
@@ -1532,11 +1549,11 @@
         <v>1</v>
       </c>
       <c r="G9" s="1">
-        <f t="shared" ref="G9:G14" si="2">$B9*1250*$D9*$F9</f>
+        <f t="shared" ref="G9:G15" si="2">$B9*1250*$D9*$F9</f>
         <v>62500</v>
       </c>
       <c r="H9" s="1">
-        <f t="shared" ref="H9:H14" si="3">$B9*1.8*$D9*IF(1-$F9=0,1,(1-$F9)*10)</f>
+        <f t="shared" ref="H9:H15" si="3">$B9*1.8*$D9*IF(1-$F9=0,1,(1-$F9)*10)</f>
         <v>90</v>
       </c>
     </row>
@@ -1632,30 +1649,60 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="B14" s="1">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="D14" s="1">
         <f>_xlfn.XLOOKUP($C14,構造係数!$A$2:$A$5,構造係数!$B$2:$B$5)</f>
         <v>5</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F14" s="1">
         <f>_xlfn.XLOOKUP($E14,舗装係数!$A$2:$A$6,舗装係数!$B$2:$B$6)</f>
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G14" s="1">
         <f t="shared" si="2"/>
+        <v>18750</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="3"/>
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="1">
+        <v>60</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="1">
+        <f>_xlfn.XLOOKUP($C15,構造係数!$A$2:$A$5,構造係数!$B$2:$B$5)</f>
+        <v>5</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="1">
+        <f>_xlfn.XLOOKUP($E15,舗装係数!$A$2:$A$6,舗装係数!$B$2:$B$6)</f>
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <f t="shared" si="2"/>
         <v>375000</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H15" s="1">
         <f t="shared" si="3"/>
         <v>540</v>
       </c>
